--- a/Testing Documentation/Control System Software Testing Sheet.xlsx
+++ b/Testing Documentation/Control System Software Testing Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Testing Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="8_{FBA2663E-ED33-4556-A16D-527C9F9C3C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8A345AB-5F03-46D8-8EC2-1FF4E09C0DDD}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="8_{FBA2663E-ED33-4556-A16D-527C9F9C3C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3265CE8-E07D-429C-98F9-ADAF610D6A2F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BF4E4ED8-54C0-4025-9CD6-5DFD3D543718}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="288">
   <si>
     <t>Cold Start Delay</t>
   </si>
@@ -900,6 +900,9 @@
   </si>
   <si>
     <t xml:space="preserve">Change in Voltage was accounted for, both shown in HMI and on </t>
+  </si>
+  <si>
+    <t>Proof</t>
   </si>
 </sst>
 </file>
@@ -991,7 +994,10 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1045,15 +1051,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F09FC7E9-3A3A-43AC-ADE0-22B9C03EF297}" name="Table1" displayName="Table1" ref="A1:G257" totalsRowShown="0">
-  <autoFilter ref="A1:G257" xr:uid="{F09FC7E9-3A3A-43AC-ADE0-22B9C03EF297}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F09FC7E9-3A3A-43AC-ADE0-22B9C03EF297}" name="Table1" displayName="Table1" ref="A1:H257" totalsRowShown="0">
+  <autoFilter ref="A1:H257" xr:uid="{F09FC7E9-3A3A-43AC-ADE0-22B9C03EF297}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{E373BA83-FDF1-4156-9DF6-71F010642680}" name="Component"/>
     <tableColumn id="2" xr3:uid="{A7EBD88B-EB3E-4561-AEF6-34D6587171B9}" name="Subcomponent"/>
     <tableColumn id="3" xr3:uid="{32849BF5-5184-4DF5-A4DF-B0F1FE5CAC17}" name="Test"/>
-    <tableColumn id="4" xr3:uid="{830BDE53-54FC-4EA2-A144-891D2FEB8C24}" name="Result" dataDxfId="0"/>
-    <tableColumn id="5" xr3:uid="{FE3A4B39-184B-45AE-9136-61404F881488}" name="Completed" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{E740D503-70A0-4F6C-BE66-D448D4817824}" name="Skid Required For Testing" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{830BDE53-54FC-4EA2-A144-891D2FEB8C24}" name="Result" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{13EB3C2E-5451-48FC-9A2E-1E301DF47B80}" name="Proof" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{FE3A4B39-184B-45AE-9136-61404F881488}" name="Completed" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{E740D503-70A0-4F6C-BE66-D448D4817824}" name="Skid Required For Testing" dataDxfId="3"/>
     <tableColumn id="7" xr3:uid="{0021E15F-6C6B-4223-9DDC-7597D35F013E}" name="Skid Components Needed"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1377,7 +1384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CEF6D7F-C2EC-451C-A2FB-CFE5672E6A58}">
-  <dimension ref="A1:G257"/>
+  <dimension ref="A1:H257"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
@@ -1386,11 +1393,11 @@
     <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.21875" customWidth="1"/>
     <col min="6" max="6" width="23.77734375" customWidth="1"/>
-    <col min="7" max="7" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="27.33203125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="30.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>184</v>
       </c>
@@ -1404,16 +1411,19 @@
         <v>154</v>
       </c>
       <c r="E1" t="s">
+        <v>287</v>
+      </c>
+      <c r="F1" t="s">
         <v>168</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>144</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>169</v>
       </c>
@@ -1424,14 +1434,15 @@
         <v>113</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="E2" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E2" s="2"/>
       <c r="F2" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G2" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>169</v>
       </c>
@@ -1442,14 +1453,15 @@
         <v>114</v>
       </c>
       <c r="D3" s="2"/>
-      <c r="E3" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E3" s="2"/>
       <c r="F3" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G3" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>169</v>
       </c>
@@ -1460,14 +1472,15 @@
         <v>140</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E4" s="2"/>
       <c r="F4" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G4" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>169</v>
       </c>
@@ -1478,14 +1491,15 @@
         <v>110</v>
       </c>
       <c r="D5" s="2"/>
-      <c r="E5" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E5" s="2"/>
       <c r="F5" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G5" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>169</v>
       </c>
@@ -1496,14 +1510,15 @@
         <v>115</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E6" s="2"/>
       <c r="F6" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G6" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>169</v>
       </c>
@@ -1514,14 +1529,15 @@
         <v>111</v>
       </c>
       <c r="D7" s="2"/>
-      <c r="E7" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E7" s="2"/>
       <c r="F7" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G7" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>169</v>
       </c>
@@ -1532,14 +1548,15 @@
         <v>117</v>
       </c>
       <c r="D8" s="2"/>
-      <c r="E8" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E8" s="2"/>
       <c r="F8" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G8" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>169</v>
       </c>
@@ -1550,14 +1567,15 @@
         <v>118</v>
       </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E9" s="2"/>
       <c r="F9" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G9" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>169</v>
       </c>
@@ -1568,14 +1586,15 @@
         <v>112</v>
       </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E10" s="2"/>
       <c r="F10" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G10" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>169</v>
       </c>
@@ -1586,14 +1605,15 @@
         <v>120</v>
       </c>
       <c r="D11" s="2"/>
-      <c r="E11" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E11" s="2"/>
       <c r="F11" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G11" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>169</v>
       </c>
@@ -1604,14 +1624,15 @@
         <v>119</v>
       </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E12" s="2"/>
       <c r="F12" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G12" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>169</v>
       </c>
@@ -1622,14 +1643,15 @@
         <v>125</v>
       </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E13" s="2"/>
       <c r="F13" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G13" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>169</v>
       </c>
@@ -1640,14 +1662,15 @@
         <v>126</v>
       </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E14" s="2"/>
       <c r="F14" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G14" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>169</v>
       </c>
@@ -1658,14 +1681,15 @@
         <v>111</v>
       </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E15" s="2"/>
       <c r="F15" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G15" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>169</v>
       </c>
@@ -1676,14 +1700,15 @@
         <v>117</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E16" s="2"/>
       <c r="F16" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>169</v>
       </c>
@@ -1694,14 +1719,15 @@
         <v>118</v>
       </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E17" s="2"/>
       <c r="F17" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>169</v>
       </c>
@@ -1712,14 +1738,15 @@
         <v>112</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E18" s="2"/>
       <c r="F18" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>169</v>
       </c>
@@ -1730,14 +1757,15 @@
         <v>120</v>
       </c>
       <c r="D19" s="2"/>
-      <c r="E19" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E19" s="2"/>
       <c r="F19" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>169</v>
       </c>
@@ -1748,14 +1776,15 @@
         <v>119</v>
       </c>
       <c r="D20" s="2"/>
-      <c r="E20" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E20" s="2"/>
       <c r="F20" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G20" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>169</v>
       </c>
@@ -1766,14 +1795,15 @@
         <v>125</v>
       </c>
       <c r="D21" s="2"/>
-      <c r="E21" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E21" s="2"/>
       <c r="F21" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G21" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>169</v>
       </c>
@@ -1784,14 +1814,15 @@
         <v>126</v>
       </c>
       <c r="D22" s="2"/>
-      <c r="E22" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E22" s="2"/>
       <c r="F22" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G22" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>169</v>
       </c>
@@ -1802,14 +1833,15 @@
         <v>116</v>
       </c>
       <c r="D23" s="2"/>
-      <c r="E23" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E23" s="2"/>
       <c r="F23" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G23" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>169</v>
       </c>
@@ -1820,14 +1852,15 @@
         <v>121</v>
       </c>
       <c r="D24" s="2"/>
-      <c r="E24" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E24" s="2"/>
       <c r="F24" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G24" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>169</v>
       </c>
@@ -1838,14 +1871,15 @@
         <v>140</v>
       </c>
       <c r="D25" s="2"/>
-      <c r="E25" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E25" s="2"/>
       <c r="F25" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G25" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>169</v>
       </c>
@@ -1856,14 +1890,15 @@
         <v>110</v>
       </c>
       <c r="D26" s="2"/>
-      <c r="E26" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E26" s="2"/>
       <c r="F26" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G26" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>169</v>
       </c>
@@ -1874,14 +1909,15 @@
         <v>115</v>
       </c>
       <c r="D27" s="2"/>
-      <c r="E27" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E27" s="2"/>
       <c r="F27" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G27" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>169</v>
       </c>
@@ -1892,14 +1928,15 @@
         <v>111</v>
       </c>
       <c r="D28" s="2"/>
-      <c r="E28" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E28" s="2"/>
       <c r="F28" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G28" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>169</v>
       </c>
@@ -1910,14 +1947,15 @@
         <v>117</v>
       </c>
       <c r="D29" s="2"/>
-      <c r="E29" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E29" s="2"/>
       <c r="F29" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G29" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>169</v>
       </c>
@@ -1928,14 +1966,15 @@
         <v>118</v>
       </c>
       <c r="D30" s="2"/>
-      <c r="E30" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E30" s="2"/>
       <c r="F30" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G30" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>169</v>
       </c>
@@ -1946,14 +1985,15 @@
         <v>112</v>
       </c>
       <c r="D31" s="2"/>
-      <c r="E31" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E31" s="2"/>
       <c r="F31" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G31" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>169</v>
       </c>
@@ -1964,14 +2004,15 @@
         <v>120</v>
       </c>
       <c r="D32" s="2"/>
-      <c r="E32" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E32" s="2"/>
       <c r="F32" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G32" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>169</v>
       </c>
@@ -1982,14 +2023,15 @@
         <v>119</v>
       </c>
       <c r="D33" s="2"/>
-      <c r="E33" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E33" s="2"/>
       <c r="F33" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G33" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>169</v>
       </c>
@@ -2000,14 +2042,15 @@
         <v>125</v>
       </c>
       <c r="D34" s="2"/>
-      <c r="E34" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E34" s="2"/>
       <c r="F34" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G34" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>169</v>
       </c>
@@ -2018,14 +2061,15 @@
         <v>128</v>
       </c>
       <c r="D35" s="2"/>
-      <c r="E35" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E35" s="2"/>
       <c r="F35" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G35" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>169</v>
       </c>
@@ -2036,14 +2080,15 @@
         <v>129</v>
       </c>
       <c r="D36" s="2"/>
-      <c r="E36" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E36" s="2"/>
       <c r="F36" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G36" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>169</v>
       </c>
@@ -2054,14 +2099,15 @@
         <v>134</v>
       </c>
       <c r="D37" s="2"/>
-      <c r="E37" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E37" s="2"/>
       <c r="F37" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G37" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>169</v>
       </c>
@@ -2072,14 +2118,15 @@
         <v>135</v>
       </c>
       <c r="D38" s="2"/>
-      <c r="E38" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E38" s="2"/>
       <c r="F38" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G38" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>169</v>
       </c>
@@ -2090,14 +2137,15 @@
         <v>136</v>
       </c>
       <c r="D39" s="2"/>
-      <c r="E39" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E39" s="2"/>
       <c r="F39" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G39" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>169</v>
       </c>
@@ -2108,14 +2156,15 @@
         <v>137</v>
       </c>
       <c r="D40" s="2"/>
-      <c r="E40" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E40" s="2"/>
       <c r="F40" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G40" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>169</v>
       </c>
@@ -2126,14 +2175,15 @@
         <v>138</v>
       </c>
       <c r="D41" s="2"/>
-      <c r="E41" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E41" s="2"/>
       <c r="F41" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G41" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>169</v>
       </c>
@@ -2144,14 +2194,15 @@
         <v>139</v>
       </c>
       <c r="D42" s="2"/>
-      <c r="E42" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E42" s="2"/>
       <c r="F42" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G42" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>170</v>
       </c>
@@ -2164,14 +2215,15 @@
       <c r="D43" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="E43" s="1" t="b">
+      <c r="E43" s="2"/>
+      <c r="F43" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F43" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G43" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>170</v>
       </c>
@@ -2182,28 +2234,30 @@
         <v>153</v>
       </c>
       <c r="D44" s="2"/>
-      <c r="E44" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E44" s="2"/>
       <c r="F44" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="G44" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C45" t="s">
         <v>285</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="E45" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E45" s="2"/>
       <c r="F45" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="G45" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>170</v>
       </c>
@@ -2216,14 +2270,15 @@
       <c r="D46" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="E46" s="1" t="b">
+      <c r="E46" s="2"/>
+      <c r="F46" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="F46" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G46" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>170</v>
       </c>
@@ -2234,14 +2289,15 @@
         <v>132</v>
       </c>
       <c r="D47" s="2"/>
-      <c r="E47" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E47" s="2"/>
       <c r="F47" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G47" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>170</v>
       </c>
@@ -2252,17 +2308,18 @@
         <v>19</v>
       </c>
       <c r="D48" s="2"/>
-      <c r="E48" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E48" s="2"/>
       <c r="F48" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>170</v>
       </c>
@@ -2273,17 +2330,18 @@
         <v>35</v>
       </c>
       <c r="D49" s="2"/>
-      <c r="E49" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E49" s="2"/>
       <c r="F49" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>170</v>
       </c>
@@ -2294,17 +2352,18 @@
         <v>14</v>
       </c>
       <c r="D50" s="2"/>
-      <c r="E50" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E50" s="2"/>
       <c r="F50" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>170</v>
       </c>
@@ -2315,17 +2374,18 @@
         <v>17</v>
       </c>
       <c r="D51" s="2"/>
-      <c r="E51" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E51" s="2"/>
       <c r="F51" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>170</v>
       </c>
@@ -2336,17 +2396,18 @@
         <v>18</v>
       </c>
       <c r="D52" s="2"/>
-      <c r="E52" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E52" s="2"/>
       <c r="F52" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>170</v>
       </c>
@@ -2357,17 +2418,18 @@
         <v>36</v>
       </c>
       <c r="D53" s="2"/>
-      <c r="E53" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E53" s="2"/>
       <c r="F53" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G53" t="s">
+      <c r="H53" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>170</v>
       </c>
@@ -2378,17 +2440,18 @@
         <v>23</v>
       </c>
       <c r="D54" s="2"/>
-      <c r="E54" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E54" s="2"/>
       <c r="F54" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G54" t="s">
+      <c r="H54" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>170</v>
       </c>
@@ -2399,17 +2462,18 @@
         <v>15</v>
       </c>
       <c r="D55" s="2"/>
-      <c r="E55" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E55" s="2"/>
       <c r="F55" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G55" t="s">
+      <c r="H55" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>170</v>
       </c>
@@ -2420,14 +2484,15 @@
         <v>20</v>
       </c>
       <c r="D56" s="2"/>
-      <c r="E56" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E56" s="2"/>
       <c r="F56" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G56" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>170</v>
       </c>
@@ -2438,14 +2503,15 @@
         <v>21</v>
       </c>
       <c r="D57" s="2"/>
-      <c r="E57" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E57" s="2"/>
       <c r="F57" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G57" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>170</v>
       </c>
@@ -2456,14 +2522,15 @@
         <v>22</v>
       </c>
       <c r="D58" s="2"/>
-      <c r="E58" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E58" s="2"/>
       <c r="F58" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G58" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>170</v>
       </c>
@@ -2474,14 +2541,15 @@
         <v>37</v>
       </c>
       <c r="D59" s="2"/>
-      <c r="E59" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E59" s="2"/>
       <c r="F59" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G59" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>170</v>
       </c>
@@ -2492,14 +2560,15 @@
         <v>38</v>
       </c>
       <c r="D60" s="2"/>
-      <c r="E60" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E60" s="2"/>
       <c r="F60" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G60" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>170</v>
       </c>
@@ -2510,14 +2579,15 @@
         <v>13</v>
       </c>
       <c r="D61" s="2"/>
-      <c r="E61" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E61" s="2"/>
       <c r="F61" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G61" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>170</v>
       </c>
@@ -2528,14 +2598,15 @@
         <v>27</v>
       </c>
       <c r="D62" s="2"/>
-      <c r="E62" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E62" s="2"/>
       <c r="F62" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G62" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>170</v>
       </c>
@@ -2546,14 +2617,15 @@
         <v>39</v>
       </c>
       <c r="D63" s="2"/>
-      <c r="E63" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E63" s="2"/>
       <c r="F63" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G63" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>170</v>
       </c>
@@ -2564,14 +2636,15 @@
         <v>28</v>
       </c>
       <c r="D64" s="2"/>
-      <c r="E64" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E64" s="2"/>
       <c r="F64" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G64" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>170</v>
       </c>
@@ -2582,14 +2655,15 @@
         <v>24</v>
       </c>
       <c r="D65" s="2"/>
-      <c r="E65" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E65" s="2"/>
       <c r="F65" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G65" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>170</v>
       </c>
@@ -2600,17 +2674,18 @@
         <v>16</v>
       </c>
       <c r="D66" s="2"/>
-      <c r="E66" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E66" s="2"/>
       <c r="F66" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>170</v>
       </c>
@@ -2621,14 +2696,15 @@
         <v>26</v>
       </c>
       <c r="D67" s="2"/>
-      <c r="E67" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E67" s="2"/>
       <c r="F67" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G67" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>170</v>
       </c>
@@ -2639,14 +2715,15 @@
         <v>40</v>
       </c>
       <c r="D68" s="2"/>
-      <c r="E68" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E68" s="2"/>
       <c r="F68" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G68" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>170</v>
       </c>
@@ -2657,14 +2734,15 @@
         <v>25</v>
       </c>
       <c r="D69" s="2"/>
-      <c r="E69" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E69" s="2"/>
       <c r="F69" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G69" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>170</v>
       </c>
@@ -2675,14 +2753,15 @@
         <v>41</v>
       </c>
       <c r="D70" s="2"/>
-      <c r="E70" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E70" s="2"/>
       <c r="F70" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G70" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>170</v>
       </c>
@@ -2693,14 +2772,15 @@
         <v>24</v>
       </c>
       <c r="D71" s="2"/>
-      <c r="E71" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E71" s="2"/>
       <c r="F71" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G71" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>170</v>
       </c>
@@ -2711,17 +2791,18 @@
         <v>16</v>
       </c>
       <c r="D72" s="2"/>
-      <c r="E72" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E72" s="2"/>
       <c r="F72" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>170</v>
       </c>
@@ -2732,14 +2813,15 @@
         <v>29</v>
       </c>
       <c r="D73" s="2"/>
-      <c r="E73" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E73" s="2"/>
       <c r="F73" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G73" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>170</v>
       </c>
@@ -2750,17 +2832,18 @@
         <v>34</v>
       </c>
       <c r="D74" s="2"/>
-      <c r="E74" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E74" s="2"/>
       <c r="F74" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G74" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G74" t="s">
+      <c r="H74" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>170</v>
       </c>
@@ -2771,14 +2854,15 @@
         <v>30</v>
       </c>
       <c r="D75" s="2"/>
-      <c r="E75" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E75" s="2"/>
       <c r="F75" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G75" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>170</v>
       </c>
@@ -2789,14 +2873,15 @@
         <v>31</v>
       </c>
       <c r="D76" s="2"/>
-      <c r="E76" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E76" s="2"/>
       <c r="F76" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G76" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>170</v>
       </c>
@@ -2807,17 +2892,18 @@
         <v>42</v>
       </c>
       <c r="D77" s="2"/>
-      <c r="E77" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E77" s="2"/>
       <c r="F77" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G77" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>170</v>
       </c>
@@ -2828,14 +2914,15 @@
         <v>32</v>
       </c>
       <c r="D78" s="2"/>
-      <c r="E78" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E78" s="2"/>
       <c r="F78" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G78" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>170</v>
       </c>
@@ -2846,14 +2933,15 @@
         <v>33</v>
       </c>
       <c r="D79" s="2"/>
-      <c r="E79" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E79" s="2"/>
       <c r="F79" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G79" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>170</v>
       </c>
@@ -2864,17 +2952,18 @@
         <v>43</v>
       </c>
       <c r="D80" s="2"/>
-      <c r="E80" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E80" s="2"/>
       <c r="F80" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G80" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G80" t="s">
+      <c r="H80" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>170</v>
       </c>
@@ -2885,14 +2974,15 @@
         <v>44</v>
       </c>
       <c r="D81" s="2"/>
-      <c r="E81" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E81" s="2"/>
       <c r="F81" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G81" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>170</v>
       </c>
@@ -2903,14 +2993,15 @@
         <v>45</v>
       </c>
       <c r="D82" s="2"/>
-      <c r="E82" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E82" s="2"/>
       <c r="F82" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G82" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>170</v>
       </c>
@@ -2921,14 +3012,15 @@
         <v>46</v>
       </c>
       <c r="D83" s="2"/>
-      <c r="E83" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E83" s="2"/>
       <c r="F83" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G83" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>170</v>
       </c>
@@ -2939,14 +3031,15 @@
         <v>50</v>
       </c>
       <c r="D84" s="2"/>
-      <c r="E84" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E84" s="2"/>
       <c r="F84" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G84" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>170</v>
       </c>
@@ -2957,14 +3050,15 @@
         <v>47</v>
       </c>
       <c r="D85" s="2"/>
-      <c r="E85" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E85" s="2"/>
       <c r="F85" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G85" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>170</v>
       </c>
@@ -2975,14 +3069,15 @@
         <v>48</v>
       </c>
       <c r="D86" s="2"/>
-      <c r="E86" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E86" s="2"/>
       <c r="F86" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G86" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>170</v>
       </c>
@@ -2993,14 +3088,15 @@
         <v>49</v>
       </c>
       <c r="D87" s="2"/>
-      <c r="E87" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E87" s="2"/>
       <c r="F87" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G87" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>170</v>
       </c>
@@ -3011,14 +3107,15 @@
         <v>51</v>
       </c>
       <c r="D88" s="2"/>
-      <c r="E88" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E88" s="2"/>
       <c r="F88" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G88" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>170</v>
       </c>
@@ -3029,14 +3126,15 @@
         <v>52</v>
       </c>
       <c r="D89" s="2"/>
-      <c r="E89" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E89" s="2"/>
       <c r="F89" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G89" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>170</v>
       </c>
@@ -3047,14 +3145,15 @@
         <v>159</v>
       </c>
       <c r="D90" s="2"/>
-      <c r="E90" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E90" s="2"/>
       <c r="F90" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G90" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>170</v>
       </c>
@@ -3065,14 +3164,15 @@
         <v>160</v>
       </c>
       <c r="D91" s="2"/>
-      <c r="E91" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E91" s="2"/>
       <c r="F91" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G91" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>170</v>
       </c>
@@ -3083,14 +3183,15 @@
         <v>161</v>
       </c>
       <c r="D92" s="2"/>
-      <c r="E92" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E92" s="2"/>
       <c r="F92" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G92" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>170</v>
       </c>
@@ -3101,14 +3202,15 @@
         <v>162</v>
       </c>
       <c r="D93" s="2"/>
-      <c r="E93" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E93" s="2"/>
       <c r="F93" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G93" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>170</v>
       </c>
@@ -3119,14 +3221,15 @@
         <v>163</v>
       </c>
       <c r="D94" s="2"/>
-      <c r="E94" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E94" s="2"/>
       <c r="F94" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G94" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>170</v>
       </c>
@@ -3137,14 +3240,15 @@
         <v>164</v>
       </c>
       <c r="D95" s="2"/>
-      <c r="E95" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E95" s="2"/>
       <c r="F95" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G95" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>170</v>
       </c>
@@ -3155,14 +3259,15 @@
         <v>146</v>
       </c>
       <c r="D96" s="2"/>
-      <c r="E96" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E96" s="2"/>
       <c r="F96" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G96" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>170</v>
       </c>
@@ -3173,14 +3278,15 @@
         <v>147</v>
       </c>
       <c r="D97" s="2"/>
-      <c r="E97" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E97" s="2"/>
       <c r="F97" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G97" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>170</v>
       </c>
@@ -3191,14 +3297,15 @@
         <v>148</v>
       </c>
       <c r="D98" s="2"/>
-      <c r="E98" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E98" s="2"/>
       <c r="F98" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G98" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>170</v>
       </c>
@@ -3209,14 +3316,15 @@
         <v>172</v>
       </c>
       <c r="D99" s="2"/>
-      <c r="E99" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E99" s="2"/>
       <c r="F99" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G99" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>170</v>
       </c>
@@ -3227,17 +3335,18 @@
         <v>173</v>
       </c>
       <c r="D100" s="2"/>
-      <c r="E100" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E100" s="2"/>
       <c r="F100" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G100" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G100" t="s">
+      <c r="H100" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>170</v>
       </c>
@@ -3248,14 +3357,15 @@
         <v>174</v>
       </c>
       <c r="D101" s="2"/>
-      <c r="E101" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E101" s="2"/>
       <c r="F101" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G101" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>170</v>
       </c>
@@ -3266,17 +3376,18 @@
         <v>175</v>
       </c>
       <c r="D102" s="2"/>
-      <c r="E102" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E102" s="2"/>
       <c r="F102" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G102" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G102" t="s">
+      <c r="H102" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>170</v>
       </c>
@@ -3287,14 +3398,15 @@
         <v>176</v>
       </c>
       <c r="D103" s="2"/>
-      <c r="E103" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E103" s="2"/>
       <c r="F103" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G103" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>170</v>
       </c>
@@ -3305,17 +3417,18 @@
         <v>177</v>
       </c>
       <c r="D104" s="2"/>
-      <c r="E104" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E104" s="2"/>
       <c r="F104" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G104" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G104" t="s">
+      <c r="H104" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>170</v>
       </c>
@@ -3326,17 +3439,18 @@
         <v>178</v>
       </c>
       <c r="D105" s="2"/>
-      <c r="E105" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E105" s="2"/>
       <c r="F105" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G105" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G105" t="s">
+      <c r="H105" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>170</v>
       </c>
@@ -3347,17 +3461,18 @@
         <v>179</v>
       </c>
       <c r="D106" s="2"/>
-      <c r="E106" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E106" s="2"/>
       <c r="F106" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G106" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G106" t="s">
+      <c r="H106" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>170</v>
       </c>
@@ -3368,17 +3483,18 @@
         <v>55</v>
       </c>
       <c r="D107" s="2"/>
-      <c r="E107" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E107" s="2"/>
       <c r="F107" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G107" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G107" t="s">
+      <c r="H107" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>170</v>
       </c>
@@ -3389,17 +3505,18 @@
         <v>155</v>
       </c>
       <c r="D108" s="2"/>
-      <c r="E108" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E108" s="2"/>
       <c r="F108" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G108" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G108" t="s">
+      <c r="H108" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>170</v>
       </c>
@@ -3410,17 +3527,18 @@
         <v>100</v>
       </c>
       <c r="D109" s="2"/>
-      <c r="E109" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E109" s="2"/>
       <c r="F109" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G109" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G109" t="s">
+      <c r="H109" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>170</v>
       </c>
@@ -3431,17 +3549,18 @@
         <v>101</v>
       </c>
       <c r="D110" s="2"/>
-      <c r="E110" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E110" s="2"/>
       <c r="F110" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G110" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G110" t="s">
+      <c r="H110" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>170</v>
       </c>
@@ -3452,14 +3571,15 @@
         <v>156</v>
       </c>
       <c r="D111" s="2"/>
-      <c r="E111" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E111" s="2"/>
       <c r="F111" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G111" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>170</v>
       </c>
@@ -3470,14 +3590,15 @@
         <v>157</v>
       </c>
       <c r="D112" s="2"/>
-      <c r="E112" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E112" s="2"/>
       <c r="F112" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G112" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>180</v>
       </c>
@@ -3488,14 +3609,15 @@
         <v>56</v>
       </c>
       <c r="D113" s="2"/>
-      <c r="E113" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E113" s="2"/>
       <c r="F113" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G113" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>180</v>
       </c>
@@ -3506,14 +3628,15 @@
         <v>57</v>
       </c>
       <c r="D114" s="2"/>
-      <c r="E114" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E114" s="2"/>
       <c r="F114" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G114" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>180</v>
       </c>
@@ -3524,14 +3647,15 @@
         <v>59</v>
       </c>
       <c r="D115" s="2"/>
-      <c r="E115" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E115" s="2"/>
       <c r="F115" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G115" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>180</v>
       </c>
@@ -3542,14 +3666,15 @@
         <v>58</v>
       </c>
       <c r="D116" s="2"/>
-      <c r="E116" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E116" s="2"/>
       <c r="F116" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G116" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>180</v>
       </c>
@@ -3560,14 +3685,15 @@
         <v>60</v>
       </c>
       <c r="D117" s="2"/>
-      <c r="E117" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E117" s="2"/>
       <c r="F117" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G117" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>180</v>
       </c>
@@ -3578,14 +3704,15 @@
         <v>61</v>
       </c>
       <c r="D118" s="2"/>
-      <c r="E118" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E118" s="2"/>
       <c r="F118" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G118" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>180</v>
       </c>
@@ -3596,14 +3723,15 @@
         <v>62</v>
       </c>
       <c r="D119" s="2"/>
-      <c r="E119" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E119" s="2"/>
       <c r="F119" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G119" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>180</v>
       </c>
@@ -3614,14 +3742,15 @@
         <v>63</v>
       </c>
       <c r="D120" s="2"/>
-      <c r="E120" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E120" s="2"/>
       <c r="F120" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G120" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>180</v>
       </c>
@@ -3632,14 +3761,15 @@
         <v>109</v>
       </c>
       <c r="D121" s="2"/>
-      <c r="E121" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E121" s="2"/>
       <c r="F121" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G121" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>180</v>
       </c>
@@ -3650,14 +3780,15 @@
         <v>60</v>
       </c>
       <c r="D122" s="2"/>
-      <c r="E122" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E122" s="2"/>
       <c r="F122" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G122" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>180</v>
       </c>
@@ -3668,14 +3799,15 @@
         <v>65</v>
       </c>
       <c r="D123" s="2"/>
-      <c r="E123" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E123" s="2"/>
       <c r="F123" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G123" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>180</v>
       </c>
@@ -3686,14 +3818,15 @@
         <v>66</v>
       </c>
       <c r="D124" s="2"/>
-      <c r="E124" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E124" s="2"/>
       <c r="F124" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G124" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>180</v>
       </c>
@@ -3704,14 +3837,15 @@
         <v>67</v>
       </c>
       <c r="D125" s="2"/>
-      <c r="E125" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E125" s="2"/>
       <c r="F125" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G125" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>180</v>
       </c>
@@ -3722,14 +3856,15 @@
         <v>68</v>
       </c>
       <c r="D126" s="2"/>
-      <c r="E126" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E126" s="2"/>
       <c r="F126" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G126" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>181</v>
       </c>
@@ -3740,17 +3875,18 @@
         <v>70</v>
       </c>
       <c r="D127" s="2"/>
-      <c r="E127" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E127" s="2"/>
       <c r="F127" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G127" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G127" t="s">
+      <c r="H127" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>181</v>
       </c>
@@ -3761,14 +3897,15 @@
         <v>85</v>
       </c>
       <c r="D128" s="2"/>
-      <c r="E128" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E128" s="2"/>
       <c r="F128" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G128" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>181</v>
       </c>
@@ -3779,14 +3916,15 @@
         <v>86</v>
       </c>
       <c r="D129" s="2"/>
-      <c r="E129" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E129" s="2"/>
       <c r="F129" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G129" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>181</v>
       </c>
@@ -3797,14 +3935,15 @@
         <v>87</v>
       </c>
       <c r="D130" s="2"/>
-      <c r="E130" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E130" s="2"/>
       <c r="F130" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G130" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>181</v>
       </c>
@@ -3815,14 +3954,15 @@
         <v>88</v>
       </c>
       <c r="D131" s="2"/>
-      <c r="E131" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E131" s="2"/>
       <c r="F131" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G131" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>181</v>
       </c>
@@ -3833,14 +3973,15 @@
         <v>105</v>
       </c>
       <c r="D132" s="2"/>
-      <c r="E132" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E132" s="2"/>
       <c r="F132" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G132" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>181</v>
       </c>
@@ -3851,14 +3992,15 @@
         <v>106</v>
       </c>
       <c r="D133" s="2"/>
-      <c r="E133" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E133" s="2"/>
       <c r="F133" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G133" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>181</v>
       </c>
@@ -3869,14 +4011,15 @@
         <v>104</v>
       </c>
       <c r="D134" s="2"/>
-      <c r="E134" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E134" s="2"/>
       <c r="F134" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G134" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>181</v>
       </c>
@@ -3887,14 +4030,15 @@
         <v>71</v>
       </c>
       <c r="D135" s="2"/>
-      <c r="E135" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E135" s="2"/>
       <c r="F135" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G135" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>181</v>
       </c>
@@ -3905,14 +4049,15 @@
         <v>89</v>
       </c>
       <c r="D136" s="2"/>
-      <c r="E136" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E136" s="2"/>
       <c r="F136" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G136" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>181</v>
       </c>
@@ -3923,14 +4068,15 @@
         <v>96</v>
       </c>
       <c r="D137" s="2"/>
-      <c r="E137" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E137" s="2"/>
       <c r="F137" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G137" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>181</v>
       </c>
@@ -3941,14 +4087,15 @@
         <v>149</v>
       </c>
       <c r="D138" s="2"/>
-      <c r="E138" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E138" s="2"/>
       <c r="F138" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G138" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>181</v>
       </c>
@@ -3959,14 +4106,15 @@
         <v>150</v>
       </c>
       <c r="D139" s="2"/>
-      <c r="E139" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E139" s="2"/>
       <c r="F139" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G139" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>181</v>
       </c>
@@ -3977,14 +4125,15 @@
         <v>151</v>
       </c>
       <c r="D140" s="2"/>
-      <c r="E140" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E140" s="2"/>
       <c r="F140" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G140" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>181</v>
       </c>
@@ -3995,14 +4144,15 @@
         <v>152</v>
       </c>
       <c r="D141" s="2"/>
-      <c r="E141" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E141" s="2"/>
       <c r="F141" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G141" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>181</v>
       </c>
@@ -4013,14 +4163,15 @@
         <v>72</v>
       </c>
       <c r="D142" s="2"/>
-      <c r="E142" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E142" s="2"/>
       <c r="F142" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G142" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>181</v>
       </c>
@@ -4031,14 +4182,15 @@
         <v>73</v>
       </c>
       <c r="D143" s="2"/>
-      <c r="E143" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E143" s="2"/>
       <c r="F143" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G143" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>181</v>
       </c>
@@ -4049,14 +4201,15 @@
         <v>122</v>
       </c>
       <c r="D144" s="2"/>
-      <c r="E144" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E144" s="2"/>
       <c r="F144" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G144" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>181</v>
       </c>
@@ -4067,14 +4220,15 @@
         <v>142</v>
       </c>
       <c r="D145" s="2"/>
-      <c r="E145" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E145" s="2"/>
       <c r="F145" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G145" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>181</v>
       </c>
@@ -4085,14 +4239,15 @@
         <v>141</v>
       </c>
       <c r="D146" s="2"/>
-      <c r="E146" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E146" s="2"/>
       <c r="F146" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G146" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>181</v>
       </c>
@@ -4103,14 +4258,15 @@
         <v>143</v>
       </c>
       <c r="D147" s="2"/>
-      <c r="E147" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E147" s="2"/>
       <c r="F147" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G147" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>181</v>
       </c>
@@ -4121,14 +4277,15 @@
         <v>108</v>
       </c>
       <c r="D148" s="2"/>
-      <c r="E148" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E148" s="2"/>
       <c r="F148" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G148" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>182</v>
       </c>
@@ -4139,14 +4296,15 @@
         <v>75</v>
       </c>
       <c r="D149" s="2"/>
-      <c r="E149" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E149" s="2"/>
       <c r="F149" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G149" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>182</v>
       </c>
@@ -4157,14 +4315,15 @@
         <v>76</v>
       </c>
       <c r="D150" s="2"/>
-      <c r="E150" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E150" s="2"/>
       <c r="F150" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G150" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>182</v>
       </c>
@@ -4175,14 +4334,15 @@
         <v>123</v>
       </c>
       <c r="D151" s="2"/>
-      <c r="E151" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E151" s="2"/>
       <c r="F151" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G151" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>182</v>
       </c>
@@ -4193,14 +4353,15 @@
         <v>124</v>
       </c>
       <c r="D152" s="2"/>
-      <c r="E152" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E152" s="2"/>
       <c r="F152" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G152" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>182</v>
       </c>
@@ -4211,14 +4372,15 @@
         <v>77</v>
       </c>
       <c r="D153" s="2"/>
-      <c r="E153" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E153" s="2"/>
       <c r="F153" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G153" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>182</v>
       </c>
@@ -4229,14 +4391,15 @@
         <v>81</v>
       </c>
       <c r="D154" s="2"/>
-      <c r="E154" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E154" s="2"/>
       <c r="F154" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G154" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>182</v>
       </c>
@@ -4247,14 +4410,15 @@
         <v>82</v>
       </c>
       <c r="D155" s="2"/>
-      <c r="E155" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E155" s="2"/>
       <c r="F155" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G155" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>182</v>
       </c>
@@ -4265,17 +4429,18 @@
         <v>13</v>
       </c>
       <c r="D156" s="2"/>
-      <c r="E156" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E156" s="2"/>
       <c r="F156" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G156" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G156" t="s">
+      <c r="H156" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>182</v>
       </c>
@@ -4286,14 +4451,15 @@
         <v>79</v>
       </c>
       <c r="D157" s="2"/>
-      <c r="E157" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E157" s="2"/>
       <c r="F157" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G157" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>182</v>
       </c>
@@ -4304,14 +4470,15 @@
         <v>80</v>
       </c>
       <c r="D158" s="2"/>
-      <c r="E158" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E158" s="2"/>
       <c r="F158" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G158" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>182</v>
       </c>
@@ -4322,14 +4489,15 @@
         <v>83</v>
       </c>
       <c r="D159" s="2"/>
-      <c r="E159" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E159" s="2"/>
       <c r="F159" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G159" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>182</v>
       </c>
@@ -4340,14 +4508,15 @@
         <v>84</v>
       </c>
       <c r="D160" s="2"/>
-      <c r="E160" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E160" s="2"/>
       <c r="F160" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G160" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>182</v>
       </c>
@@ -4358,17 +4527,18 @@
         <v>13</v>
       </c>
       <c r="D161" s="2"/>
-      <c r="E161" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E161" s="2"/>
       <c r="F161" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G161" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G161" t="s">
+      <c r="H161" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>183</v>
       </c>
@@ -4379,17 +4549,18 @@
         <v>90</v>
       </c>
       <c r="D162" s="2"/>
-      <c r="E162" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E162" s="2"/>
       <c r="F162" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G162" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G162" t="s">
+      <c r="H162" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>183</v>
       </c>
@@ -4400,17 +4571,18 @@
         <v>91</v>
       </c>
       <c r="D163" s="2"/>
-      <c r="E163" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E163" s="2"/>
       <c r="F163" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G163" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G163" t="s">
+      <c r="H163" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>183</v>
       </c>
@@ -4421,17 +4593,18 @@
         <v>102</v>
       </c>
       <c r="D164" s="2"/>
-      <c r="E164" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E164" s="2"/>
       <c r="F164" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G164" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G164" t="s">
+      <c r="H164" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>183</v>
       </c>
@@ -4442,17 +4615,18 @@
         <v>103</v>
       </c>
       <c r="D165" s="2"/>
-      <c r="E165" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E165" s="2"/>
       <c r="F165" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G165" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G165" t="s">
+      <c r="H165" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>183</v>
       </c>
@@ -4463,17 +4637,18 @@
         <v>195</v>
       </c>
       <c r="D166" s="2"/>
-      <c r="E166" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E166" s="2"/>
       <c r="F166" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G166" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G166" t="s">
+      <c r="H166" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>183</v>
       </c>
@@ -4484,17 +4659,18 @@
         <v>92</v>
       </c>
       <c r="D167" s="2"/>
-      <c r="E167" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E167" s="2"/>
       <c r="F167" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G167" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G167" t="s">
+      <c r="H167" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>183</v>
       </c>
@@ -4505,17 +4681,18 @@
         <v>93</v>
       </c>
       <c r="D168" s="2"/>
-      <c r="E168" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E168" s="2"/>
       <c r="F168" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G168" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G168" t="s">
+      <c r="H168" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>183</v>
       </c>
@@ -4526,17 +4703,18 @@
         <v>97</v>
       </c>
       <c r="D169" s="2"/>
-      <c r="E169" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E169" s="2"/>
       <c r="F169" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G169" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G169" t="s">
+      <c r="H169" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>183</v>
       </c>
@@ -4547,17 +4725,18 @@
         <v>13</v>
       </c>
       <c r="D170" s="2"/>
-      <c r="E170" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E170" s="2"/>
       <c r="F170" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G170" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G170" t="s">
+      <c r="H170" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>183</v>
       </c>
@@ -4568,17 +4747,18 @@
         <v>94</v>
       </c>
       <c r="D171" s="2"/>
-      <c r="E171" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E171" s="2"/>
       <c r="F171" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G171" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G171" t="s">
+      <c r="H171" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>183</v>
       </c>
@@ -4589,17 +4769,18 @@
         <v>95</v>
       </c>
       <c r="D172" s="2"/>
-      <c r="E172" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E172" s="2"/>
       <c r="F172" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G172" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G172" t="s">
+      <c r="H172" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>183</v>
       </c>
@@ -4610,17 +4791,18 @@
         <v>92</v>
       </c>
       <c r="D173" s="2"/>
-      <c r="E173" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E173" s="2"/>
       <c r="F173" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G173" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G173" t="s">
+      <c r="H173" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>183</v>
       </c>
@@ -4631,17 +4813,18 @@
         <v>93</v>
       </c>
       <c r="D174" s="2"/>
-      <c r="E174" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E174" s="2"/>
       <c r="F174" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G174" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G174" t="s">
+      <c r="H174" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>183</v>
       </c>
@@ -4652,17 +4835,18 @@
         <v>97</v>
       </c>
       <c r="D175" s="2"/>
-      <c r="E175" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E175" s="2"/>
       <c r="F175" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G175" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G175" t="s">
+      <c r="H175" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>183</v>
       </c>
@@ -4673,17 +4857,18 @@
         <v>13</v>
       </c>
       <c r="D176" s="2"/>
-      <c r="E176" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E176" s="2"/>
       <c r="F176" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G176" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G176" t="s">
+      <c r="H176" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
         <v>201</v>
       </c>
@@ -4694,14 +4879,15 @@
         <v>202</v>
       </c>
       <c r="D177" s="2"/>
-      <c r="E177" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E177" s="2"/>
       <c r="F177" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G177" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
         <v>201</v>
       </c>
@@ -4712,14 +4898,15 @@
         <v>203</v>
       </c>
       <c r="D178" s="2"/>
-      <c r="E178" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E178" s="2"/>
       <c r="F178" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G178" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
         <v>201</v>
       </c>
@@ -4730,14 +4917,15 @@
         <v>204</v>
       </c>
       <c r="D179" s="2"/>
-      <c r="E179" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E179" s="2"/>
       <c r="F179" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G179" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
         <v>201</v>
       </c>
@@ -4748,14 +4936,15 @@
         <v>205</v>
       </c>
       <c r="D180" s="2"/>
-      <c r="E180" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E180" s="2"/>
       <c r="F180" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G180" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
         <v>201</v>
       </c>
@@ -4766,14 +4955,15 @@
         <v>206</v>
       </c>
       <c r="D181" s="2"/>
-      <c r="E181" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E181" s="2"/>
       <c r="F181" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G181" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
         <v>201</v>
       </c>
@@ -4784,14 +4974,15 @@
         <v>207</v>
       </c>
       <c r="D182" s="2"/>
-      <c r="E182" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E182" s="2"/>
       <c r="F182" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G182" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
         <v>201</v>
       </c>
@@ -4802,14 +4993,15 @@
         <v>208</v>
       </c>
       <c r="D183" s="2"/>
-      <c r="E183" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E183" s="2"/>
       <c r="F183" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G183" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
         <v>201</v>
       </c>
@@ -4820,14 +5012,15 @@
         <v>209</v>
       </c>
       <c r="D184" s="2"/>
-      <c r="E184" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E184" s="2"/>
       <c r="F184" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G184" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
         <v>201</v>
       </c>
@@ -4838,14 +5031,15 @@
         <v>210</v>
       </c>
       <c r="D185" s="2"/>
-      <c r="E185" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E185" s="2"/>
       <c r="F185" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G185" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
         <v>201</v>
       </c>
@@ -4856,14 +5050,15 @@
         <v>211</v>
       </c>
       <c r="D186" s="2"/>
-      <c r="E186" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E186" s="2"/>
       <c r="F186" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G186" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
         <v>201</v>
       </c>
@@ -4874,14 +5069,15 @@
         <v>212</v>
       </c>
       <c r="D187" s="2"/>
-      <c r="E187" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E187" s="2"/>
       <c r="F187" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G187" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
         <v>201</v>
       </c>
@@ -4892,14 +5088,15 @@
         <v>213</v>
       </c>
       <c r="D188" s="2"/>
-      <c r="E188" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E188" s="2"/>
       <c r="F188" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G188" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
         <v>201</v>
       </c>
@@ -4910,14 +5107,15 @@
         <v>214</v>
       </c>
       <c r="D189" s="2"/>
-      <c r="E189" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E189" s="2"/>
       <c r="F189" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G189" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
         <v>201</v>
       </c>
@@ -4928,14 +5126,15 @@
         <v>215</v>
       </c>
       <c r="D190" s="2"/>
-      <c r="E190" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E190" s="2"/>
       <c r="F190" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G190" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
         <v>201</v>
       </c>
@@ -4946,14 +5145,15 @@
         <v>216</v>
       </c>
       <c r="D191" s="2"/>
-      <c r="E191" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E191" s="2"/>
       <c r="F191" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G191" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
         <v>201</v>
       </c>
@@ -4964,14 +5164,15 @@
         <v>217</v>
       </c>
       <c r="D192" s="2"/>
-      <c r="E192" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E192" s="2"/>
       <c r="F192" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G192" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
         <v>201</v>
       </c>
@@ -4982,14 +5183,15 @@
         <v>218</v>
       </c>
       <c r="D193" s="2"/>
-      <c r="E193" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E193" s="2"/>
       <c r="F193" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G193" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
         <v>201</v>
       </c>
@@ -5000,14 +5202,15 @@
         <v>219</v>
       </c>
       <c r="D194" s="2"/>
-      <c r="E194" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E194" s="2"/>
       <c r="F194" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G194" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
         <v>201</v>
       </c>
@@ -5018,14 +5221,15 @@
         <v>220</v>
       </c>
       <c r="D195" s="2"/>
-      <c r="E195" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E195" s="2"/>
       <c r="F195" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G195" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
         <v>201</v>
       </c>
@@ -5036,14 +5240,15 @@
         <v>221</v>
       </c>
       <c r="D196" s="2"/>
-      <c r="E196" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E196" s="2"/>
       <c r="F196" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G196" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
         <v>201</v>
       </c>
@@ -5054,14 +5259,15 @@
         <v>222</v>
       </c>
       <c r="D197" s="2"/>
-      <c r="E197" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E197" s="2"/>
       <c r="F197" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G197" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
         <v>201</v>
       </c>
@@ -5072,14 +5278,15 @@
         <v>223</v>
       </c>
       <c r="D198" s="2"/>
-      <c r="E198" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E198" s="2"/>
       <c r="F198" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G198" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
         <v>201</v>
       </c>
@@ -5090,14 +5297,15 @@
         <v>224</v>
       </c>
       <c r="D199" s="2"/>
-      <c r="E199" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E199" s="2"/>
       <c r="F199" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G199" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
         <v>201</v>
       </c>
@@ -5108,14 +5316,15 @@
         <v>225</v>
       </c>
       <c r="D200" s="2"/>
-      <c r="E200" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E200" s="2"/>
       <c r="F200" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G200" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
         <v>201</v>
       </c>
@@ -5126,14 +5335,15 @@
         <v>226</v>
       </c>
       <c r="D201" s="2"/>
-      <c r="E201" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E201" s="2"/>
       <c r="F201" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G201" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
         <v>201</v>
       </c>
@@ -5144,14 +5354,15 @@
         <v>227</v>
       </c>
       <c r="D202" s="2"/>
-      <c r="E202" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E202" s="2"/>
       <c r="F202" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G202" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
         <v>201</v>
       </c>
@@ -5162,14 +5373,15 @@
         <v>228</v>
       </c>
       <c r="D203" s="2"/>
-      <c r="E203" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E203" s="2"/>
       <c r="F203" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G203" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
         <v>201</v>
       </c>
@@ -5180,14 +5392,15 @@
         <v>229</v>
       </c>
       <c r="D204" s="2"/>
-      <c r="E204" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E204" s="2"/>
       <c r="F204" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G204" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
         <v>201</v>
       </c>
@@ -5198,14 +5411,15 @@
         <v>230</v>
       </c>
       <c r="D205" s="2"/>
-      <c r="E205" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E205" s="2"/>
       <c r="F205" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G205" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
         <v>201</v>
       </c>
@@ -5216,14 +5430,15 @@
         <v>231</v>
       </c>
       <c r="D206" s="2"/>
-      <c r="E206" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E206" s="2"/>
       <c r="F206" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G206" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
         <v>201</v>
       </c>
@@ -5234,14 +5449,15 @@
         <v>232</v>
       </c>
       <c r="D207" s="2"/>
-      <c r="E207" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E207" s="2"/>
       <c r="F207" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G207" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
         <v>201</v>
       </c>
@@ -5252,14 +5468,15 @@
         <v>233</v>
       </c>
       <c r="D208" s="2"/>
-      <c r="E208" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E208" s="2"/>
       <c r="F208" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G208" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
         <v>201</v>
       </c>
@@ -5270,14 +5487,15 @@
         <v>234</v>
       </c>
       <c r="D209" s="2"/>
-      <c r="E209" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E209" s="2"/>
       <c r="F209" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G209" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
         <v>201</v>
       </c>
@@ -5288,14 +5506,15 @@
         <v>235</v>
       </c>
       <c r="D210" s="2"/>
-      <c r="E210" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E210" s="2"/>
       <c r="F210" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G210" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
         <v>201</v>
       </c>
@@ -5306,14 +5525,15 @@
         <v>236</v>
       </c>
       <c r="D211" s="2"/>
-      <c r="E211" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E211" s="2"/>
       <c r="F211" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G211" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
         <v>201</v>
       </c>
@@ -5324,14 +5544,15 @@
         <v>237</v>
       </c>
       <c r="D212" s="2"/>
-      <c r="E212" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E212" s="2"/>
       <c r="F212" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G212" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
         <v>201</v>
       </c>
@@ -5342,14 +5563,15 @@
         <v>238</v>
       </c>
       <c r="D213" s="2"/>
-      <c r="E213" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E213" s="2"/>
       <c r="F213" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G213" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
         <v>201</v>
       </c>
@@ -5360,14 +5582,15 @@
         <v>239</v>
       </c>
       <c r="D214" s="2"/>
-      <c r="E214" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E214" s="2"/>
       <c r="F214" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G214" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
         <v>201</v>
       </c>
@@ -5378,14 +5601,15 @@
         <v>240</v>
       </c>
       <c r="D215" s="2"/>
-      <c r="E215" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E215" s="2"/>
       <c r="F215" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G215" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
         <v>201</v>
       </c>
@@ -5396,14 +5620,15 @@
         <v>241</v>
       </c>
       <c r="D216" s="2"/>
-      <c r="E216" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E216" s="2"/>
       <c r="F216" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G216" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
         <v>201</v>
       </c>
@@ -5414,14 +5639,15 @@
         <v>242</v>
       </c>
       <c r="D217" s="2"/>
-      <c r="E217" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E217" s="2"/>
       <c r="F217" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G217" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
         <v>201</v>
       </c>
@@ -5432,14 +5658,15 @@
         <v>243</v>
       </c>
       <c r="D218" s="2"/>
-      <c r="E218" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E218" s="2"/>
       <c r="F218" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G218" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
         <v>201</v>
       </c>
@@ -5450,14 +5677,15 @@
         <v>244</v>
       </c>
       <c r="D219" s="2"/>
-      <c r="E219" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E219" s="2"/>
       <c r="F219" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G219" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
         <v>201</v>
       </c>
@@ -5468,14 +5696,15 @@
         <v>245</v>
       </c>
       <c r="D220" s="2"/>
-      <c r="E220" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E220" s="2"/>
       <c r="F220" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G220" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
         <v>201</v>
       </c>
@@ -5486,14 +5715,15 @@
         <v>246</v>
       </c>
       <c r="D221" s="2"/>
-      <c r="E221" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E221" s="2"/>
       <c r="F221" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G221" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
         <v>201</v>
       </c>
@@ -5504,14 +5734,15 @@
         <v>247</v>
       </c>
       <c r="D222" s="2"/>
-      <c r="E222" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E222" s="2"/>
       <c r="F222" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G222" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
         <v>201</v>
       </c>
@@ -5522,14 +5753,15 @@
         <v>248</v>
       </c>
       <c r="D223" s="2"/>
-      <c r="E223" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E223" s="2"/>
       <c r="F223" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G223" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
         <v>201</v>
       </c>
@@ -5540,14 +5772,15 @@
         <v>249</v>
       </c>
       <c r="D224" s="2"/>
-      <c r="E224" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E224" s="2"/>
       <c r="F224" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G224" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
         <v>201</v>
       </c>
@@ -5558,14 +5791,15 @@
         <v>250</v>
       </c>
       <c r="D225" s="2"/>
-      <c r="E225" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E225" s="2"/>
       <c r="F225" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G225" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
         <v>201</v>
       </c>
@@ -5576,14 +5810,15 @@
         <v>251</v>
       </c>
       <c r="D226" s="2"/>
-      <c r="E226" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E226" s="2"/>
       <c r="F226" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G226" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
         <v>201</v>
       </c>
@@ -5594,14 +5829,15 @@
         <v>252</v>
       </c>
       <c r="D227" s="2"/>
-      <c r="E227" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E227" s="2"/>
       <c r="F227" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G227" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
         <v>201</v>
       </c>
@@ -5612,14 +5848,15 @@
         <v>253</v>
       </c>
       <c r="D228" s="2"/>
-      <c r="E228" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E228" s="2"/>
       <c r="F228" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G228" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
         <v>201</v>
       </c>
@@ -5630,14 +5867,15 @@
         <v>254</v>
       </c>
       <c r="D229" s="2"/>
-      <c r="E229" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E229" s="2"/>
       <c r="F229" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G229" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
         <v>201</v>
       </c>
@@ -5648,14 +5886,15 @@
         <v>255</v>
       </c>
       <c r="D230" s="2"/>
-      <c r="E230" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E230" s="2"/>
       <c r="F230" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G230" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
         <v>201</v>
       </c>
@@ -5666,14 +5905,15 @@
         <v>256</v>
       </c>
       <c r="D231" s="2"/>
-      <c r="E231" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E231" s="2"/>
       <c r="F231" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G231" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
         <v>201</v>
       </c>
@@ -5684,14 +5924,15 @@
         <v>257</v>
       </c>
       <c r="D232" s="2"/>
-      <c r="E232" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E232" s="2"/>
       <c r="F232" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G232" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
         <v>201</v>
       </c>
@@ -5702,14 +5943,15 @@
         <v>258</v>
       </c>
       <c r="D233" s="2"/>
-      <c r="E233" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E233" s="2"/>
       <c r="F233" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G233" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
         <v>201</v>
       </c>
@@ -5720,14 +5962,15 @@
         <v>259</v>
       </c>
       <c r="D234" s="2"/>
-      <c r="E234" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E234" s="2"/>
       <c r="F234" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G234" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
         <v>201</v>
       </c>
@@ -5738,14 +5981,15 @@
         <v>260</v>
       </c>
       <c r="D235" s="2"/>
-      <c r="E235" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E235" s="2"/>
       <c r="F235" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G235" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
         <v>201</v>
       </c>
@@ -5756,14 +6000,15 @@
         <v>261</v>
       </c>
       <c r="D236" s="2"/>
-      <c r="E236" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E236" s="2"/>
       <c r="F236" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G236" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
         <v>201</v>
       </c>
@@ -5774,14 +6019,15 @@
         <v>262</v>
       </c>
       <c r="D237" s="2"/>
-      <c r="E237" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E237" s="2"/>
       <c r="F237" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G237" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
         <v>201</v>
       </c>
@@ -5792,14 +6038,15 @@
         <v>263</v>
       </c>
       <c r="D238" s="2"/>
-      <c r="E238" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E238" s="2"/>
       <c r="F238" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G238" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
         <v>201</v>
       </c>
@@ -5810,14 +6057,15 @@
         <v>264</v>
       </c>
       <c r="D239" s="2"/>
-      <c r="E239" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E239" s="2"/>
       <c r="F239" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G239" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
         <v>201</v>
       </c>
@@ -5828,14 +6076,15 @@
         <v>265</v>
       </c>
       <c r="D240" s="2"/>
-      <c r="E240" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E240" s="2"/>
       <c r="F240" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G240" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
         <v>201</v>
       </c>
@@ -5846,14 +6095,15 @@
         <v>266</v>
       </c>
       <c r="D241" s="2"/>
-      <c r="E241" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E241" s="2"/>
       <c r="F241" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G241" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
         <v>201</v>
       </c>
@@ -5864,14 +6114,15 @@
         <v>267</v>
       </c>
       <c r="D242" s="2"/>
-      <c r="E242" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E242" s="2"/>
       <c r="F242" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G242" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
         <v>201</v>
       </c>
@@ -5882,14 +6133,15 @@
         <v>268</v>
       </c>
       <c r="D243" s="2"/>
-      <c r="E243" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E243" s="2"/>
       <c r="F243" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G243" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" s="3" t="s">
         <v>201</v>
       </c>
@@ -5900,14 +6152,15 @@
         <v>269</v>
       </c>
       <c r="D244" s="2"/>
-      <c r="E244" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E244" s="2"/>
       <c r="F244" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G244" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
         <v>201</v>
       </c>
@@ -5918,14 +6171,15 @@
         <v>270</v>
       </c>
       <c r="D245" s="2"/>
-      <c r="E245" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E245" s="2"/>
       <c r="F245" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G245" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
         <v>201</v>
       </c>
@@ -5936,14 +6190,15 @@
         <v>271</v>
       </c>
       <c r="D246" s="2"/>
-      <c r="E246" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E246" s="2"/>
       <c r="F246" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G246" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
         <v>201</v>
       </c>
@@ -5954,14 +6209,15 @@
         <v>272</v>
       </c>
       <c r="D247" s="2"/>
-      <c r="E247" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E247" s="2"/>
       <c r="F247" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G247" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" s="3" t="s">
         <v>201</v>
       </c>
@@ -5972,14 +6228,15 @@
         <v>273</v>
       </c>
       <c r="D248" s="2"/>
-      <c r="E248" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E248" s="2"/>
       <c r="F248" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G248" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
         <v>201</v>
       </c>
@@ -5990,14 +6247,15 @@
         <v>274</v>
       </c>
       <c r="D249" s="2"/>
-      <c r="E249" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E249" s="2"/>
       <c r="F249" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G249" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" s="3" t="s">
         <v>201</v>
       </c>
@@ -6008,14 +6266,15 @@
         <v>275</v>
       </c>
       <c r="D250" s="2"/>
-      <c r="E250" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E250" s="2"/>
       <c r="F250" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G250" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
         <v>201</v>
       </c>
@@ -6026,14 +6285,15 @@
         <v>276</v>
       </c>
       <c r="D251" s="2"/>
-      <c r="E251" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E251" s="2"/>
       <c r="F251" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G251" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" s="3" t="s">
         <v>201</v>
       </c>
@@ -6044,14 +6304,15 @@
         <v>277</v>
       </c>
       <c r="D252" s="2"/>
-      <c r="E252" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E252" s="2"/>
       <c r="F252" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G252" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
         <v>201</v>
       </c>
@@ -6062,14 +6323,15 @@
         <v>278</v>
       </c>
       <c r="D253" s="2"/>
-      <c r="E253" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E253" s="2"/>
       <c r="F253" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G253" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" s="3" t="s">
         <v>201</v>
       </c>
@@ -6080,14 +6342,15 @@
         <v>279</v>
       </c>
       <c r="D254" s="2"/>
-      <c r="E254" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E254" s="2"/>
       <c r="F254" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G254" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
         <v>201</v>
       </c>
@@ -6098,14 +6361,15 @@
         <v>280</v>
       </c>
       <c r="D255" s="2"/>
-      <c r="E255" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E255" s="2"/>
       <c r="F255" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G255" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" s="3" t="s">
         <v>201</v>
       </c>
@@ -6116,14 +6380,15 @@
         <v>281</v>
       </c>
       <c r="D256" s="2"/>
-      <c r="E256" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E256" s="2"/>
       <c r="F256" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G256" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
         <v>201</v>
       </c>
@@ -6134,10 +6399,11 @@
         <v>282</v>
       </c>
       <c r="D257" s="2"/>
-      <c r="E257" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="E257" s="2"/>
       <c r="F257" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G257" s="1" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Testing Documentation/Control System Software Testing Sheet.xlsx
+++ b/Testing Documentation/Control System Software Testing Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Testing Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="8_{FBA2663E-ED33-4556-A16D-527C9F9C3C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3265CE8-E07D-429C-98F9-ADAF610D6A2F}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="8_{FBA2663E-ED33-4556-A16D-527C9F9C3C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CFF4966-3639-4C67-AF4B-4E5241D61ACA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BF4E4ED8-54C0-4025-9CD6-5DFD3D543718}"/>
   </bookViews>
@@ -987,20 +987,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
@@ -1014,6 +1008,12 @@
           <xfpb:DXFComplement i="0"/>
         </ext>
       </extLst>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1050,6 +1050,10 @@
 </FeaturePropertyBags>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F09FC7E9-3A3A-43AC-ADE0-22B9C03EF297}" name="Table1" displayName="Table1" ref="A1:H257" totalsRowShown="0">
   <autoFilter ref="A1:H257" xr:uid="{F09FC7E9-3A3A-43AC-ADE0-22B9C03EF297}"/>
@@ -1057,10 +1061,10 @@
     <tableColumn id="1" xr3:uid="{E373BA83-FDF1-4156-9DF6-71F010642680}" name="Component"/>
     <tableColumn id="2" xr3:uid="{A7EBD88B-EB3E-4561-AEF6-34D6587171B9}" name="Subcomponent"/>
     <tableColumn id="3" xr3:uid="{32849BF5-5184-4DF5-A4DF-B0F1FE5CAC17}" name="Test"/>
-    <tableColumn id="4" xr3:uid="{830BDE53-54FC-4EA2-A144-891D2FEB8C24}" name="Result" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{13EB3C2E-5451-48FC-9A2E-1E301DF47B80}" name="Proof" dataDxfId="0"/>
-    <tableColumn id="5" xr3:uid="{FE3A4B39-184B-45AE-9136-61404F881488}" name="Completed" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{E740D503-70A0-4F6C-BE66-D448D4817824}" name="Skid Required For Testing" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{830BDE53-54FC-4EA2-A144-891D2FEB8C24}" name="Result" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{13EB3C2E-5451-48FC-9A2E-1E301DF47B80}" name="Proof" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{FE3A4B39-184B-45AE-9136-61404F881488}" name="Completed" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{E740D503-70A0-4F6C-BE66-D448D4817824}" name="Skid Required For Testing" dataDxfId="0"/>
     <tableColumn id="7" xr3:uid="{0021E15F-6C6B-4223-9DDC-7597D35F013E}" name="Skid Components Needed"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3782,7 +3786,7 @@
       <c r="D122" s="2"/>
       <c r="E122" s="2"/>
       <c r="F122" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" s="1" t="b">
         <v>0</v>
@@ -3801,7 +3805,7 @@
       <c r="D123" s="2"/>
       <c r="E123" s="2"/>
       <c r="F123" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G123" s="1" t="b">
         <v>0</v>

--- a/Testing Documentation/Control System Software Testing Sheet.xlsx
+++ b/Testing Documentation/Control System Software Testing Sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96325486694b1ce6/Documents/GitHub/TMEIC-DI-Water-Cooling-Skid-Repo/Testing Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="8_{FBA2663E-ED33-4556-A16D-527C9F9C3C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CFF4966-3639-4C67-AF4B-4E5241D61ACA}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="8_{FBA2663E-ED33-4556-A16D-527C9F9C3C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8235C6F4-9930-4666-9528-5EED4AEF863B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BF4E4ED8-54C0-4025-9CD6-5DFD3D543718}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="291">
   <si>
     <t>Cold Start Delay</t>
   </si>
@@ -893,9 +893,6 @@
     <t>Voltage from multimeter observed</t>
   </si>
   <si>
-    <t>Current from ,multimeter observed</t>
-  </si>
-  <si>
     <t>Voltage Measurement Dynamics</t>
   </si>
   <si>
@@ -903,6 +900,18 @@
   </si>
   <si>
     <t>Proof</t>
+  </si>
+  <si>
+    <t>Enabled Manual Fan Mode on HMI. Able to control fan 1 and fan 2. Disabling allowed automatic control</t>
+  </si>
+  <si>
+    <t>When pump lifcycle is engaged, automatic pump switching occurs, per the increment</t>
+  </si>
+  <si>
+    <t>Automatic lifecycle is disengaged when Simplex Mode is active</t>
+  </si>
+  <si>
+    <t>Current from multimeter observed</t>
   </si>
 </sst>
 </file>
@@ -1415,7 +1424,7 @@
         <v>154</v>
       </c>
       <c r="E1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F1" t="s">
         <v>168</v>
@@ -2248,10 +2257,10 @@
     </row>
     <row r="45" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="C45" t="s">
+        <v>284</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="1" t="b">
@@ -2272,7 +2281,7 @@
         <v>131</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="1" t="b">
@@ -3773,7 +3782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>180</v>
       </c>
@@ -3783,7 +3792,9 @@
       <c r="C122" t="s">
         <v>60</v>
       </c>
-      <c r="D122" s="2"/>
+      <c r="D122" s="2" t="s">
+        <v>288</v>
+      </c>
       <c r="E122" s="2"/>
       <c r="F122" s="1" t="b">
         <v>1</v>
@@ -3792,7 +3803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>180</v>
       </c>
@@ -3802,7 +3813,9 @@
       <c r="C123" t="s">
         <v>65</v>
       </c>
-      <c r="D123" s="2"/>
+      <c r="D123" s="2" t="s">
+        <v>289</v>
+      </c>
       <c r="E123" s="2"/>
       <c r="F123" s="1" t="b">
         <v>1</v>
@@ -4175,7 +4188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>181</v>
       </c>
@@ -4185,10 +4198,12 @@
       <c r="C143" t="s">
         <v>73</v>
       </c>
-      <c r="D143" s="2"/>
+      <c r="D143" s="2" t="s">
+        <v>287</v>
+      </c>
       <c r="E143" s="2"/>
       <c r="F143" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" s="1" t="b">
         <v>0</v>
